--- a/testdata/configuration.xlsx
+++ b/testdata/configuration.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10187"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -143,7 +143,7 @@
     <t>dev</t>
   </si>
   <si>
-    <t>https://test.dbp.nlbkb.rs/login</t>
+    <t>https://uat.dbp.nlbkb.rs/login</t>
   </si>
   <si>
     <t>Chrome</t>
@@ -161,10 +161,10 @@
     <t>1</t>
   </si>
   <si>
-    <t>si.nlb.klik.uat:id/</t>
-  </si>
-  <si>
-    <t>si.nlb.klik.uat</t>
+    <t>rs.nlb.klik.uat:id/</t>
+  </si>
+  <si>
+    <t>rs.nlb.klik.uat</t>
   </si>
   <si>
     <t>si.nlb.klik.RootActivity</t>
@@ -1331,6 +1331,7 @@
     <col min="8" max="9" width="22.5740740740741" customWidth="1"/>
     <col min="10" max="12" width="31.712962962963" customWidth="1"/>
     <col min="13" max="13" width="16.4259259259259" customWidth="1"/>
+    <col min="14" max="14" width="22.5555555555556" customWidth="1"/>
     <col min="20" max="20" width="16.4259259259259" customWidth="1"/>
     <col min="21" max="21" width="12.287037037037" customWidth="1"/>
     <col min="31" max="31" width="16" customWidth="1"/>
@@ -1566,7 +1567,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="AF2" r:id="rId1" display="bozidar.tomasevic@dtc.rs"/>
-    <hyperlink ref="C2" r:id="rId2" display="https://test.dbp.nlbkb.rs/login" tooltip="https://test.dbp.nlbkb.rs/login"/>
+    <hyperlink ref="C2" r:id="rId2" display="https://uat.dbp.nlbkb.rs/login" tooltip="https://uat.dbp.nlbkb.rs/login"/>
     <hyperlink ref="AI2" r:id="rId3" display="\\10.11.1.158\03. TEST Team\NLB SLO\FileShare\UAT" tooltip="\\10.11.1.158\03. TEST Team\NLB SLO\FileShare\UAT"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testdata/configuration.xlsx
+++ b/testdata/configuration.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="10187"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -143,7 +143,7 @@
     <t>dev</t>
   </si>
   <si>
-    <t>https://uat.dbp.nlbkb.rs/login</t>
+    <t>https://test.dbp.nlbkb.rs/login</t>
   </si>
   <si>
     <t>Chrome</t>
@@ -161,10 +161,10 @@
     <t>1</t>
   </si>
   <si>
-    <t>rs.nlb.klik.uat:id/</t>
-  </si>
-  <si>
-    <t>rs.nlb.klik.uat</t>
+    <t>si.nlb.klik.uat:id/</t>
+  </si>
+  <si>
+    <t>si.nlb.klik.uat</t>
   </si>
   <si>
     <t>si.nlb.klik.RootActivity</t>
@@ -1331,7 +1331,6 @@
     <col min="8" max="9" width="22.5740740740741" customWidth="1"/>
     <col min="10" max="12" width="31.712962962963" customWidth="1"/>
     <col min="13" max="13" width="16.4259259259259" customWidth="1"/>
-    <col min="14" max="14" width="22.5555555555556" customWidth="1"/>
     <col min="20" max="20" width="16.4259259259259" customWidth="1"/>
     <col min="21" max="21" width="12.287037037037" customWidth="1"/>
     <col min="31" max="31" width="16" customWidth="1"/>
@@ -1567,7 +1566,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="AF2" r:id="rId1" display="bozidar.tomasevic@dtc.rs"/>
-    <hyperlink ref="C2" r:id="rId2" display="https://uat.dbp.nlbkb.rs/login" tooltip="https://uat.dbp.nlbkb.rs/login"/>
+    <hyperlink ref="C2" r:id="rId2" display="https://test.dbp.nlbkb.rs/login" tooltip="https://test.dbp.nlbkb.rs/login"/>
     <hyperlink ref="AI2" r:id="rId3" display="\\10.11.1.158\03. TEST Team\NLB SLO\FileShare\UAT" tooltip="\\10.11.1.158\03. TEST Team\NLB SLO\FileShare\UAT"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testdata/configuration.xlsx
+++ b/testdata/configuration.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10187"/>
+    <workbookView windowWidth="20490" windowHeight="7500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1321,20 +1321,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AK2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="9.22222222222222" customWidth="1"/>
+    <col min="1" max="1" width="9.21904761904762" customWidth="1"/>
     <col min="2" max="2" width="13.3333333333333" customWidth="1"/>
-    <col min="3" max="3" width="28.1111111111111" customWidth="1"/>
-    <col min="4" max="5" width="22.5555555555556" customWidth="1"/>
+    <col min="3" max="3" width="28.1142857142857" customWidth="1"/>
+    <col min="4" max="5" width="22.552380952381" customWidth="1"/>
     <col min="7" max="7" width="20.3333333333333" customWidth="1"/>
-    <col min="8" max="9" width="22.5740740740741" customWidth="1"/>
-    <col min="10" max="12" width="31.712962962963" customWidth="1"/>
-    <col min="13" max="13" width="16.4259259259259" customWidth="1"/>
-    <col min="20" max="20" width="16.4259259259259" customWidth="1"/>
-    <col min="21" max="21" width="12.287037037037" customWidth="1"/>
+    <col min="8" max="9" width="22.5714285714286" customWidth="1"/>
+    <col min="10" max="12" width="31.7142857142857" customWidth="1"/>
+    <col min="13" max="13" width="16.4285714285714" customWidth="1"/>
+    <col min="20" max="20" width="16.4285714285714" customWidth="1"/>
+    <col min="21" max="21" width="12.2857142857143" customWidth="1"/>
     <col min="31" max="31" width="16" customWidth="1"/>
-    <col min="32" max="32" width="17.712962962963" customWidth="1"/>
+    <col min="32" max="32" width="17.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37">

--- a/testdata/configuration.xlsx
+++ b/testdata/configuration.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -143,7 +143,7 @@
     <t>dev</t>
   </si>
   <si>
-    <t>https://test.dbp.nlbkb.rs/login</t>
+    <t>https://uat.dbp.nlbkb.rs/login</t>
   </si>
   <si>
     <t>Chrome</t>
@@ -161,10 +161,10 @@
     <t>1</t>
   </si>
   <si>
-    <t>si.nlb.klik.uat:id/</t>
-  </si>
-  <si>
-    <t>si.nlb.klik.uat</t>
+    <t>rs.nlb.klik.uat:id/</t>
+  </si>
+  <si>
+    <t>rs.nlb.klik.uat</t>
   </si>
   <si>
     <t>si.nlb.klik.RootActivity</t>
@@ -914,17 +914,17 @@
     <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -946,7 +946,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1321,20 +1321,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AK2"/>
-  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="9.21904761904762" customWidth="1"/>
+    <col min="1" max="1" width="9.22222222222222" customWidth="1"/>
     <col min="2" max="2" width="13.3333333333333" customWidth="1"/>
-    <col min="3" max="3" width="28.1142857142857" customWidth="1"/>
-    <col min="4" max="5" width="22.552380952381" customWidth="1"/>
+    <col min="3" max="3" width="28.1111111111111" customWidth="1"/>
+    <col min="4" max="5" width="22.5555555555556" customWidth="1"/>
     <col min="7" max="7" width="20.3333333333333" customWidth="1"/>
-    <col min="8" max="9" width="22.5714285714286" customWidth="1"/>
-    <col min="10" max="12" width="31.7142857142857" customWidth="1"/>
-    <col min="13" max="13" width="16.4285714285714" customWidth="1"/>
-    <col min="20" max="20" width="16.4285714285714" customWidth="1"/>
-    <col min="21" max="21" width="12.2857142857143" customWidth="1"/>
+    <col min="8" max="9" width="22.5740740740741" customWidth="1"/>
+    <col min="10" max="12" width="31.712962962963" customWidth="1"/>
+    <col min="13" max="13" width="16.4259259259259" customWidth="1"/>
+    <col min="14" max="14" width="22.5555555555556" customWidth="1"/>
+    <col min="20" max="20" width="16.4259259259259" customWidth="1"/>
+    <col min="21" max="21" width="12.287037037037" customWidth="1"/>
     <col min="31" max="31" width="16" customWidth="1"/>
-    <col min="32" max="32" width="17.7142857142857" customWidth="1"/>
+    <col min="32" max="32" width="17.712962962963" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37">
@@ -1362,46 +1363,46 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="7" t="s">
+      <c r="T1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="7" t="s">
+      <c r="U1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="7" t="s">
+      <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
       <c r="W1" s="1" t="s">
@@ -1443,10 +1444,10 @@
       <c r="AI1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="4" t="s">
+      <c r="AJ1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="4" t="s">
+      <c r="AK1" s="5" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1457,7 +1458,7 @@
       <c r="B2" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="6" t="s">
         <v>38</v>
       </c>
       <c r="D2" t="s">
@@ -1466,7 +1467,7 @@
       <c r="E2" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>41</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -1475,37 +1476,37 @@
       <c r="H2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="Q2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="R2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="S2" s="3" t="s">
         <v>53</v>
       </c>
       <c r="T2" s="8" t="s">
@@ -1556,17 +1557,17 @@
       <c r="AI2" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="AJ2" s="4" t="s">
+      <c r="AJ2" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="AK2" s="4" t="s">
+      <c r="AK2" s="5" t="s">
         <v>62</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="AF2" r:id="rId1" display="bozidar.tomasevic@dtc.rs"/>
-    <hyperlink ref="C2" r:id="rId2" display="https://test.dbp.nlbkb.rs/login" tooltip="https://test.dbp.nlbkb.rs/login"/>
+    <hyperlink ref="C2" r:id="rId2" display="https://uat.dbp.nlbkb.rs/login" tooltip="https://uat.dbp.nlbkb.rs/login"/>
     <hyperlink ref="AI2" r:id="rId3" display="\\10.11.1.158\03. TEST Team\NLB SLO\FileShare\UAT" tooltip="\\10.11.1.158\03. TEST Team\NLB SLO\FileShare\UAT"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testdata/configuration.xlsx
+++ b/testdata/configuration.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="10187"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -143,7 +143,7 @@
     <t>dev</t>
   </si>
   <si>
-    <t>https://uat.dbp.nlbkb.rs/login</t>
+    <t>https://test.dbp.nlbkb.rs/login</t>
   </si>
   <si>
     <t>Chrome</t>
@@ -161,10 +161,10 @@
     <t>1</t>
   </si>
   <si>
-    <t>rs.nlb.klik.uat:id/</t>
-  </si>
-  <si>
-    <t>rs.nlb.klik.uat</t>
+    <t>si.nlb.klik.uat:id/</t>
+  </si>
+  <si>
+    <t>si.nlb.klik.uat</t>
   </si>
   <si>
     <t>si.nlb.klik.RootActivity</t>
@@ -914,17 +914,17 @@
     <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -946,7 +946,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1331,7 +1331,6 @@
     <col min="8" max="9" width="22.5740740740741" customWidth="1"/>
     <col min="10" max="12" width="31.712962962963" customWidth="1"/>
     <col min="13" max="13" width="16.4259259259259" customWidth="1"/>
-    <col min="14" max="14" width="22.5555555555556" customWidth="1"/>
     <col min="20" max="20" width="16.4259259259259" customWidth="1"/>
     <col min="21" max="21" width="12.287037037037" customWidth="1"/>
     <col min="31" max="31" width="16" customWidth="1"/>
@@ -1363,46 +1362,46 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="V1" s="7" t="s">
         <v>21</v>
       </c>
       <c r="W1" s="1" t="s">
@@ -1444,10 +1443,10 @@
       <c r="AI1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="5" t="s">
+      <c r="AJ1" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="5" t="s">
+      <c r="AK1" s="4" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1458,7 +1457,7 @@
       <c r="B2" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D2" t="s">
@@ -1467,7 +1466,7 @@
       <c r="E2" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>41</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -1476,37 +1475,37 @@
       <c r="H2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N2" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="P2" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="Q2" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="R2" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="S2" s="5" t="s">
         <v>53</v>
       </c>
       <c r="T2" s="8" t="s">
@@ -1557,17 +1556,17 @@
       <c r="AI2" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="AJ2" s="5" t="s">
+      <c r="AJ2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AK2" s="5" t="s">
+      <c r="AK2" s="4" t="s">
         <v>62</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="AF2" r:id="rId1" display="bozidar.tomasevic@dtc.rs"/>
-    <hyperlink ref="C2" r:id="rId2" display="https://uat.dbp.nlbkb.rs/login" tooltip="https://uat.dbp.nlbkb.rs/login"/>
+    <hyperlink ref="C2" r:id="rId2" display="https://test.dbp.nlbkb.rs/login" tooltip="https://test.dbp.nlbkb.rs/login"/>
     <hyperlink ref="AI2" r:id="rId3" display="\\10.11.1.158\03. TEST Team\NLB SLO\FileShare\UAT" tooltip="\\10.11.1.158\03. TEST Team\NLB SLO\FileShare\UAT"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testdata/configuration.xlsx
+++ b/testdata/configuration.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10187"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="64">
   <si>
     <t>Order</t>
   </si>
@@ -161,13 +161,16 @@
     <t>1</t>
   </si>
   <si>
+    <t>rs.nlb.klik.tst:id/</t>
+  </si>
+  <si>
+    <t>rs.nlb.klik.test</t>
+  </si>
+  <si>
+    <t>si.nlb.klik.RootActivity</t>
+  </si>
+  <si>
     <t>si.nlb.klik.uat:id/</t>
-  </si>
-  <si>
-    <t>si.nlb.klik.uat</t>
-  </si>
-  <si>
-    <t>si.nlb.klik.RootActivity</t>
   </si>
   <si>
     <t>emulator-5554</t>
@@ -914,17 +917,17 @@
     <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -946,7 +949,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1362,46 +1365,46 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="7" t="s">
+      <c r="T1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="7" t="s">
+      <c r="U1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="7" t="s">
+      <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
       <c r="W1" s="1" t="s">
@@ -1443,10 +1446,10 @@
       <c r="AI1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="4" t="s">
+      <c r="AJ1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="4" t="s">
+      <c r="AK1" s="5" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1457,7 +1460,7 @@
       <c r="B2" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="6" t="s">
         <v>38</v>
       </c>
       <c r="D2" t="s">
@@ -1466,7 +1469,7 @@
       <c r="E2" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>41</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -1475,92 +1478,92 @@
       <c r="H2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="L2" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="M2" s="5" t="s">
+      <c r="L2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="M2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="N2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="O2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="P2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="Q2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="R2" s="3" t="s">
         <v>53</v>
       </c>
+      <c r="S2" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="T2" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U2" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V2" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="W2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="X2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Y2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Z2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AA2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AB2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AC2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AD2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AE2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AF2" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AG2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AH2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AI2" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ2" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="AJ2" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="AK2" s="4" t="s">
-        <v>62</v>
+      <c r="AK2" s="5" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
